--- a/public/assets/template_excel/template_unggah_pegawai_poltekbang.xlsx
+++ b/public/assets/template_excel/template_unggah_pegawai_poltekbang.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PPTI\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\onn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD368462-C068-4E7F-8A8C-B19EE318C2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0395C6-DB09-4954-B1AC-88476B385F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{82115587-5BD9-4A3A-9AE1-D97C143AB15A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{82115587-5BD9-4A3A-9AE1-D97C143AB15A}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Isian" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet" sheetId="2" r:id="rId2"/>
+    <sheet name="Ref" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
   <si>
     <t>nip</t>
   </si>
@@ -78,17 +76,244 @@
     <t>kode status keaktifan</t>
   </si>
   <si>
-    <t>kode unit</t>
+    <t>123456789123456789</t>
+  </si>
+  <si>
+    <t>agus</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>1994-01-01</t>
+  </si>
+  <si>
+    <t>Surabaya</t>
+  </si>
+  <si>
+    <t>1234567812345678</t>
+  </si>
+  <si>
+    <t>0987654321</t>
+  </si>
+  <si>
+    <t>agus@gmail.com</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>60943815-0ef4-403e-98d8-7a96ecdc6d5f</t>
+  </si>
+  <si>
+    <t>b06cabe9-6376-4010-9838-9bc8d05cb173</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>idagama</t>
+  </si>
+  <si>
+    <t>namaagama</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>Kristen</t>
+  </si>
+  <si>
+    <t>Katolik</t>
+  </si>
+  <si>
+    <t>Hindu</t>
+  </si>
+  <si>
+    <t>Budha</t>
+  </si>
+  <si>
+    <t>Kepercayaan Terhadap Tuhan YME</t>
+  </si>
+  <si>
+    <t>Tidak Diisi</t>
+  </si>
+  <si>
+    <t>id_jns_sdm</t>
+  </si>
+  <si>
+    <t>nm_jns_sdm</t>
+  </si>
+  <si>
+    <t>Dosen</t>
+  </si>
+  <si>
+    <t>316e6e79-abef-4f0a-bda0-59514fe456bd</t>
+  </si>
+  <si>
+    <t>2c590af6-f9df-4038-ad3d-8a3848d26d8f</t>
+  </si>
+  <si>
+    <t>Tenaga Kependidikan</t>
+  </si>
+  <si>
+    <t>kode</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Belum Menikah</t>
+  </si>
+  <si>
+    <t>Menikah</t>
+  </si>
+  <si>
+    <t>namastatuspegawai</t>
+  </si>
+  <si>
+    <t>CPNS</t>
+  </si>
+  <si>
+    <t>Kontrak Universitas</t>
+  </si>
+  <si>
+    <t>Kontrak Program Studi</t>
+  </si>
+  <si>
+    <t>PPNPN</t>
+  </si>
+  <si>
+    <t>PNS</t>
+  </si>
+  <si>
+    <t>coba</t>
+  </si>
+  <si>
+    <t>PPPK</t>
+  </si>
+  <si>
+    <t>588fe662-9f66-44e3-a923-5056b67536f5</t>
+  </si>
+  <si>
+    <t>2a7a2da9-3221-4e8b-ba68-60907703a4b6</t>
+  </si>
+  <si>
+    <t>ca138c33-dbc7-4a0b-ace8-ed88389b50e5</t>
+  </si>
+  <si>
+    <t>02c38bb0-9478-4069-aec8-dbef502ec42f</t>
+  </si>
+  <si>
+    <t>eb592b52-58d8-4dfc-ac7d-c41c7cea695e</t>
+  </si>
+  <si>
+    <t>65653ac1-1ad7-40f3-a85e-e90e3e05b47b</t>
+  </si>
+  <si>
+    <t>6e6caa43-8be9-4fcf-9467-0b0001d7ff45</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>idstatusaktif</t>
+  </si>
+  <si>
+    <t>namastatusaktif</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Aktif</t>
+  </si>
+  <si>
+    <t>Lain-lain</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Mutasi/Pindah</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Pensiun</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Mengundurkan Diri</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Wafat</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>Pensiun Dini</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>Tugas Belajar</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Diberhentikan</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Masa Persiapan Pensiun (MPP)</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>Dipekerjakan</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>CLTN</t>
+  </si>
+  <si>
+    <t>Tidak Diketahui</t>
+  </si>
+  <si>
+    <t>juita</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -111,14 +336,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -135,7 +363,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -431,22 +659,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197DDEC2-7D1D-478C-A728-B206D4387F5E}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="3" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="18.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.86328125" style="1"/>
+    <col min="3" max="3" width="11.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.265625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="10.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,20 +717,349 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{75ACBA46-15F1-4CAB-A15C-228CD44047B6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9BD113-8E2E-4C3B-B128-98D0D6CF5256}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="28.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="M11" t="s">
+        <v>77</v>
+      </c>
+      <c r="N11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="M12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="M13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="M14" t="s">
+        <v>83</v>
+      </c>
+      <c r="N14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="M15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="M16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>